--- a/R/ROADMAP.xlsx
+++ b/R/ROADMAP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352095D0-7AA0-433A-BA87-C9C428F1886A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8047143-BC20-47EA-BC7B-85E4FF46A6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1185" yWindow="1605" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -609,7 +609,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -620,14 +620,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13.5"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -654,11 +646,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -948,735 +937,809 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A5:J40"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" customWidth="1"/>
-    <col min="4" max="4" width="36.28515625" customWidth="1"/>
-    <col min="5" max="5" width="48.42578125" customWidth="1"/>
-    <col min="6" max="6" width="31.28515625" customWidth="1"/>
-    <col min="7" max="7" width="26.7109375" customWidth="1"/>
-    <col min="8" max="8" width="20.85546875" customWidth="1"/>
-    <col min="9" max="9" width="31.42578125" customWidth="1"/>
+    <col min="1" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="37.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" customWidth="1"/>
+    <col min="5" max="5" width="36.28515625" customWidth="1"/>
+    <col min="6" max="6" width="48.42578125" customWidth="1"/>
+    <col min="7" max="7" width="31.28515625" customWidth="1"/>
+    <col min="8" max="8" width="26.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="31.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-    </row>
-    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="2">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="2">
+        <v>20</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="2">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>6</v>
+      </c>
       <c r="C7" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>3</v>
+        <v>44</v>
+      </c>
+      <c r="D7" s="2">
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="H7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="B8" s="2">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="2">
+        <v>25</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>1</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="2">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="2">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="C8" s="3">
+      <c r="B10" s="2">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="2">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="2">
+        <v>25</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="2">
+        <v>25</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="B13" s="2">
         <v>12</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="C13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="2">
+        <v>25</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="B14" s="2">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="2">
+        <v>25</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="B15" s="2">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="2">
+        <v>25</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
-        <v>2</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="B16" s="2">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="2">
+        <v>20</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="C9" s="3">
-        <v>15</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="B17" s="2">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" s="2">
+        <v>30</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="B18" s="2">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18" s="2">
+        <v>30</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="B19" s="2">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D19" s="2">
+        <v>35</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="B20" s="2">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" s="2">
         <v>20</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="E20" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" s="2">
+        <v>30</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="B22" s="2">
+        <v>21</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D22" s="2">
+        <v>40</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>3</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="3">
-        <v>15</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>4</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="3">
-        <v>20</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>5</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="3">
-        <v>18</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>6</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="3">
-        <v>15</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>7</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="3">
-        <v>25</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>8</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="3">
-        <v>20</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>9</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="3">
-        <v>18</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>10</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="3">
-        <v>25</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <v>11</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="3">
-        <v>25</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+      <c r="B23" s="2">
+        <v>22</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D23" s="2">
         <v>12</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" s="3">
-        <v>25</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>13</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" s="3">
-        <v>25</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>14</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" s="3">
-        <v>25</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>15</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C22" s="3">
-        <v>20</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
-        <v>16</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C23" s="3">
-        <v>30</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <v>17</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C24" s="3">
-        <v>30</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <v>18</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C25" s="3">
-        <v>35</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
-        <v>19</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C26" s="3">
-        <v>20</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
-        <v>20</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C27" s="3">
-        <v>30</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
-        <v>21</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C28" s="3">
-        <v>40</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
-        <v>22</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C29" s="3">
-        <v>12</v>
-      </c>
-      <c r="D29" s="3" t="s">
+      <c r="E23" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="F23" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="G23" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="H23" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="I23" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="J23" s="2" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="B28" s="3"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="4"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="B32" s="3"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
         <v>158</v>
       </c>
+      <c r="B34" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
